--- a/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 19,52</t>
+          <t>8,83; 19,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 14,04</t>
+          <t>3,65; 13,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 17,58</t>
+          <t>7,18; 18,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 6,82</t>
+          <t>-10,46; 6,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,87; 42,42</t>
+          <t>17,34; 41,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 24,51</t>
+          <t>5,58; 23,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,98; 35,54</t>
+          <t>13,11; 36,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 16,19</t>
+          <t>-21,43; 15,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 21,1</t>
+          <t>11,6; 20,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,9; 21,4</t>
+          <t>12,23; 21,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,87; 18,76</t>
+          <t>9,1; 18,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 33,51</t>
+          <t>6,5; 32,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,28; 45,33</t>
+          <t>22,22; 45,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,93; 41,0</t>
+          <t>21,45; 41,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 38,53</t>
+          <t>16,91; 36,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 196,49</t>
+          <t>15,22; 173,47</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 19,8</t>
+          <t>9,08; 19,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 22,77</t>
+          <t>12,12; 22,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 16,57</t>
+          <t>6,48; 16,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 34,54</t>
+          <t>-1,44; 36,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,88; 42,13</t>
+          <t>17,58; 43,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,18; 47,98</t>
+          <t>22,65; 48,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,13; 35,86</t>
+          <t>12,58; 35,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 84,86</t>
+          <t>-3,23; 92,74</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 21,0</t>
+          <t>12,58; 21,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 15,27</t>
+          <t>6,31; 14,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 12,66</t>
+          <t>3,96; 12,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 9,23</t>
+          <t>-5,41; 9,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,51; 47,43</t>
+          <t>25,99; 48,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 27,88</t>
+          <t>10,44; 27,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 23,82</t>
+          <t>6,87; 22,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 25,63</t>
+          <t>-12,64; 26,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,35; 18,09</t>
+          <t>13,46; 18,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,8</t>
+          <t>11,37; 16,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,72</t>
+          <t>9,32; 14,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 21,15</t>
+          <t>3,8; 22,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,26; 38,54</t>
+          <t>27,03; 38,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,91; 29,0</t>
+          <t>19,95; 29,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 26,82</t>
+          <t>17,34; 27,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 65,91</t>
+          <t>9,46; 65,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 19,2</t>
+          <t>9,28; 19,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 13,73</t>
+          <t>3,92; 13,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 18,07</t>
+          <t>6,91; 17,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 6,52</t>
+          <t>0,84; 10,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 41,42</t>
+          <t>18,3; 42,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 23,67</t>
+          <t>6,16; 23,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,11; 36,05</t>
+          <t>12,57; 35,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 15,38</t>
+          <t>1,76; 27,27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,62</t>
+          <t>8,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,88</t>
+          <t>11,94; 21,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,23; 21,23</t>
+          <t>12,36; 21,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 18,0</t>
+          <t>9,16; 17,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 32,59</t>
+          <t>4,43; 13,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,22; 45,31</t>
+          <t>23,77; 46,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,45; 41,4</t>
+          <t>21,64; 40,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,91; 36,55</t>
+          <t>17,21; 36,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 173,47</t>
+          <t>10,75; 35,91</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,51</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 19,84</t>
+          <t>9,37; 19,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,12; 22,66</t>
+          <t>12,21; 22,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,45</t>
+          <t>6,07; 16,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 36,47</t>
+          <t>-2,01; 8,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 43,02</t>
+          <t>18,32; 41,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,65; 48,48</t>
+          <t>22,51; 46,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,58; 35,84</t>
+          <t>12,12; 36,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 92,74</t>
+          <t>-4,21; 22,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,58; 21,05</t>
+          <t>12,29; 20,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 14,87</t>
+          <t>5,75; 14,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 12,23</t>
+          <t>4,0; 13,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 9,56</t>
+          <t>4,1; 12,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,99; 48,09</t>
+          <t>25,1; 47,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 27,0</t>
+          <t>9,4; 26,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 22,93</t>
+          <t>6,96; 24,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 26,0</t>
+          <t>10,61; 37,58</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,46; 18,0</t>
+          <t>13,23; 18,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 16,16</t>
+          <t>11,17; 16,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 14,0</t>
+          <t>9,02; 13,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 22,19</t>
+          <t>4,48; 9,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 38,58</t>
+          <t>26,86; 38,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,95; 29,61</t>
+          <t>19,68; 29,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,34; 27,43</t>
+          <t>17,1; 27,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 65,97</t>
+          <t>10,97; 24,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
